--- a/sample-project2/srcs/CSharp_ASPNET/build/test-results/ui-regeneration/boundaries/selected-employee.xlsx
+++ b/sample-project2/srcs/CSharp_ASPNET/build/test-results/ui-regeneration/boundaries/selected-employee.xlsx
@@ -26,13 +26,13 @@
     <x:t>2026年10月30日現在</x:t>
   </x:si>
   <x:si>
-    <x:t>作成日時（JST）：2026年10月30日 02:36</x:t>
+    <x:t>作成日時（JST）：2026年10月30日 10:18</x:t>
   </x:si>
   <x:si>
     <x:t>氏名</x:t>
   </x:si>
   <x:si>
-    <x:t>山田 太郎 通信確認9（ヤマダ タロウ）</x:t>
+    <x:t>山田 太郎 通信確認11（ヤマダ タロウ）</x:t>
   </x:si>
   <x:si>
     <x:t>社員番号・所属</x:t>
@@ -68,13 +68,13 @@
     <x:t>案件経歴</x:t>
   </x:si>
   <x:si>
-    <x:t>山田 太郎 通信確認9 ／ 2026年10月30日現在</x:t>
+    <x:t>山田 太郎 通信確認11 ／ 2026年10月30日現在</x:t>
   </x:si>
   <x:si>
     <x:t>案件連番・案件名</x:t>
   </x:si>
   <x:si>
-    <x:t>01　UI-PENDING-SAVE-8</x:t>
+    <x:t>01　UI-PENDING-SAVE-10</x:t>
   </x:si>
   <x:si>
     <x:t>期間</x:t>
@@ -975,14 +975,14 @@
   <x:pageSetup paperSize="9" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
     <x:oddHeader/>
-    <x:oddFooter>&amp;C山田 太郎 通信確認9
-職務経歴書 ／ 作成日時（JST）：2026年10月30日 02:36&amp;R&amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;C山田 太郎 通信確認11
+職務経歴書 ／ 作成日時（JST）：2026年10月30日 10:18&amp;R&amp;P / &amp;N</x:oddFooter>
     <x:evenHeader/>
-    <x:evenFooter>&amp;C山田 太郎 通信確認9
-職務経歴書 ／ 作成日時（JST）：2026年10月30日 02:36&amp;R&amp;P / &amp;N</x:evenFooter>
+    <x:evenFooter>&amp;C山田 太郎 通信確認11
+職務経歴書 ／ 作成日時（JST）：2026年10月30日 10:18&amp;R&amp;P / &amp;N</x:evenFooter>
     <x:firstHeader/>
-    <x:firstFooter>&amp;C山田 太郎 通信確認9
-職務経歴書 ／ 作成日時（JST）：2026年10月30日 02:36&amp;R&amp;P / &amp;N</x:firstFooter>
+    <x:firstFooter>&amp;C山田 太郎 通信確認11
+職務経歴書 ／ 作成日時（JST）：2026年10月30日 10:18&amp;R&amp;P / &amp;N</x:firstFooter>
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
@@ -1670,14 +1670,14 @@
   <x:pageSetup paperSize="9" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
     <x:oddHeader/>
-    <x:oddFooter>&amp;C山田 太郎 通信確認9
-案件経歴 ／ 作成日時（JST）：2026年10月30日 02:36&amp;R&amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;C山田 太郎 通信確認11
+案件経歴 ／ 作成日時（JST）：2026年10月30日 10:18&amp;R&amp;P / &amp;N</x:oddFooter>
     <x:evenHeader/>
-    <x:evenFooter>&amp;C山田 太郎 通信確認9
-案件経歴 ／ 作成日時（JST）：2026年10月30日 02:36&amp;R&amp;P / &amp;N</x:evenFooter>
+    <x:evenFooter>&amp;C山田 太郎 通信確認11
+案件経歴 ／ 作成日時（JST）：2026年10月30日 10:18&amp;R&amp;P / &amp;N</x:evenFooter>
     <x:firstHeader/>
-    <x:firstFooter>&amp;C山田 太郎 通信確認9
-案件経歴 ／ 作成日時（JST）：2026年10月30日 02:36&amp;R&amp;P / &amp;N</x:firstFooter>
+    <x:firstFooter>&amp;C山田 太郎 通信確認11
+案件経歴 ／ 作成日時（JST）：2026年10月30日 10:18&amp;R&amp;P / &amp;N</x:firstFooter>
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
